--- a/tests/testdata/excel/ファイル名/読み取り専用属性.xlsx
+++ b/tests/testdata/excel/ファイル名/読み取り専用属性.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\test\AppData\Local\Temp\win_grep_testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B672FAAB-907F-40F4-8D85-02513E63A64E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F0B1B58A-6A37-4209-A419-F9B8452485A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="10515" xr2:uid="{5ADFF189-3B8E-4375-826F-1BF100901805}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="10515" xr2:uid="{B3B3890A-195E-469C-92A9-2D76C17EE961}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -433,7 +433,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4519D0E3-02B1-41BC-893E-DCBAFDE52A00}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52BDE69A-FFC0-48E1-8A33-34517F40A8D3}">
   <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>

--- a/tests/testdata/excel/ファイル名/読み取り専用属性.xlsx
+++ b/tests/testdata/excel/ファイル名/読み取り専用属性.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\test\AppData\Local\Temp\win_grep_testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F0B1B58A-6A37-4209-A419-F9B8452485A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CA3BBF30-9765-4657-82CF-3E123AB0891A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="10515" xr2:uid="{B3B3890A-195E-469C-92A9-2D76C17EE961}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="10515" xr2:uid="{EB1B4F0E-6D8E-4035-888B-C2CA2160E514}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -433,7 +433,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52BDE69A-FFC0-48E1-8A33-34517F40A8D3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF5927C5-01D4-432F-9E7D-25478D091199}">
   <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
